--- a/InstancedModels/Results/StripPacking-BranchSP/results-StripPacking-BranchSP.xlsx
+++ b/InstancedModels/Results/StripPacking-BranchSP/results-StripPacking-BranchSP.xlsx
@@ -326,7 +326,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="20">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="0.00000000000000000"/>
     <numFmt numFmtId="165" formatCode="00.0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
@@ -345,8 +345,7 @@
     <numFmt numFmtId="179" formatCode="000.0000000000000"/>
     <numFmt numFmtId="180" formatCode="000.000000000000"/>
     <numFmt numFmtId="181" formatCode="0000000.0"/>
-    <numFmt numFmtId="182" formatCode="0.00000000000000"/>
-    <numFmt numFmtId="183" formatCode="0.0E+00"/>
+    <numFmt numFmtId="182" formatCode="0.0E+00"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -388,7 +387,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
@@ -412,8 +411,7 @@
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="181" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="182" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -423,23 +421,20 @@
     <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="0" fillId="3" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="183" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="182" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="183" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="183" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="182" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -912,13 +907,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="2" max="2" width="10.421875"/>
     <col customWidth="1" min="12" max="12" width="21.57421875"/>
     <col customWidth="1" min="14" max="14" width="17.7109375"/>
     <col customWidth="1" min="15" max="15" width="17.57421875"/>
     <col bestFit="1" min="16" max="16" width="17.28125"/>
+    <col customWidth="1" min="18" max="18" width="17.8515625"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3679,194 +3675,209 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="s">
+      <c r="A63" s="19" t="s">
         <v>78</v>
       </c>
       <c r="B63" s="1">
-        <v>45989</v>
-      </c>
-      <c r="D63" t="s">
+        <v>46002</v>
+      </c>
+      <c r="C63" s="19"/>
+      <c r="D63" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="E63" t="s">
-        <v>17</v>
-      </c>
-      <c r="F63">
+      <c r="E63" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" s="19">
         <v>35</v>
       </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
-      <c r="I63">
-        <v>1</v>
-      </c>
-      <c r="J63">
-        <v>1</v>
-      </c>
-      <c r="K63">
+      <c r="G63" s="19">
+        <v>0</v>
+      </c>
+      <c r="H63" s="19"/>
+      <c r="I63" s="19">
+        <v>1</v>
+      </c>
+      <c r="J63" s="19">
+        <v>1</v>
+      </c>
+      <c r="K63" s="19">
         <v>1</v>
       </c>
       <c r="L63" s="10">
-        <v>3600.0606459999999</v>
-      </c>
+        <v>3600.0343079999998</v>
+      </c>
+      <c r="M63" s="19"/>
       <c r="N63" s="7">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="O63" s="3">
         <v>48</v>
       </c>
       <c r="P63" s="11">
-        <v>0.51515200000000005</v>
-      </c>
-      <c r="Q63">
-        <v>10</v>
-      </c>
-      <c r="R63" s="9">
-        <v>20920</v>
+        <v>0.48936200000000002</v>
+      </c>
+      <c r="Q63" s="19">
+        <v>10</v>
+      </c>
+      <c r="R63" s="12">
+        <v>110279</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s">
+      <c r="A64" s="19" t="s">
         <v>79</v>
       </c>
       <c r="B64" s="1">
-        <v>45989</v>
-      </c>
-      <c r="D64" t="s">
+        <v>46002</v>
+      </c>
+      <c r="C64" s="19"/>
+      <c r="D64" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="E64" t="s">
-        <v>17</v>
-      </c>
-      <c r="F64">
+      <c r="E64" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64" s="19">
         <v>50</v>
       </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>1</v>
-      </c>
-      <c r="K64">
+      <c r="G64" s="19">
+        <v>0</v>
+      </c>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19">
+        <v>0</v>
+      </c>
+      <c r="J64" s="19">
+        <v>1</v>
+      </c>
+      <c r="K64" s="19">
         <v>0</v>
       </c>
       <c r="L64" s="10">
-        <v>3600.1080160000001</v>
-      </c>
+        <v>3600.0738919999999</v>
+      </c>
+      <c r="M64" s="19"/>
       <c r="N64" s="15">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="O64" s="3">
+        <v>48</v>
+      </c>
+      <c r="P64" s="11">
+        <v>0.694268</v>
+      </c>
+      <c r="Q64" s="19">
+        <v>10</v>
+      </c>
+      <c r="R64" s="12">
+        <v>286549</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B65" s="1">
+        <v>46002</v>
+      </c>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="19">
         <v>50</v>
       </c>
-      <c r="P64" s="11">
-        <v>0.69879500000000005</v>
-      </c>
-      <c r="Q64">
-        <v>10</v>
-      </c>
-      <c r="R64" s="9">
-        <v>58958</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>80</v>
-      </c>
-      <c r="B65" s="1">
-        <v>45989</v>
-      </c>
-      <c r="D65" t="s">
-        <v>69</v>
-      </c>
-      <c r="E65" t="s">
-        <v>17</v>
-      </c>
-      <c r="F65">
-        <v>50</v>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>1</v>
-      </c>
-      <c r="J65">
-        <v>1</v>
-      </c>
-      <c r="K65">
-        <v>1</v>
-      </c>
-      <c r="L65" s="14">
-        <v>3600.172188</v>
-      </c>
+      <c r="G65" s="19">
+        <v>0</v>
+      </c>
+      <c r="H65" s="19"/>
+      <c r="I65" s="19">
+        <v>1</v>
+      </c>
+      <c r="J65" s="19">
+        <v>1</v>
+      </c>
+      <c r="K65" s="19">
+        <v>1</v>
+      </c>
+      <c r="L65" s="10">
+        <v>3600.1201270000001</v>
+      </c>
+      <c r="M65" s="19"/>
       <c r="N65" s="8">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="O65" s="3">
         <v>35</v>
       </c>
       <c r="P65" s="11">
-        <v>0.79041899999999998</v>
-      </c>
-      <c r="Q65">
-        <v>10</v>
-      </c>
-      <c r="R65" s="3">
-        <v>15</v>
+        <v>0.77124199999999998</v>
+      </c>
+      <c r="Q65" s="19">
+        <v>10</v>
+      </c>
+      <c r="R65" s="5">
+        <v>3369</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="21"/>
-      <c r="B66" s="1"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
-      <c r="I66" s="21"/>
-      <c r="J66" s="21"/>
-      <c r="K66" s="21"/>
-      <c r="L66" s="14"/>
-      <c r="N66" s="8"/>
-      <c r="O66" s="3"/>
-      <c r="P66" s="11"/>
-      <c r="Q66" s="21"/>
-      <c r="R66" s="3"/>
+      <c r="A66" s="19"/>
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="19"/>
+      <c r="K66" s="19"/>
+      <c r="L66" s="19"/>
+      <c r="M66" s="19"/>
+      <c r="N66" s="19"/>
+      <c r="O66" s="19"/>
+      <c r="P66" s="19"/>
+      <c r="Q66" s="19"/>
+      <c r="R66" s="19"/>
     </row>
     <row r="67">
-      <c r="A67" t="s">
+      <c r="A67" s="19" t="s">
         <v>81</v>
       </c>
       <c r="B67" s="1">
-        <v>45989</v>
-      </c>
-      <c r="D67" t="s">
+        <v>46002</v>
+      </c>
+      <c r="C67" s="19"/>
+      <c r="D67" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E67" t="s">
-        <v>17</v>
-      </c>
-      <c r="F67">
-        <v>10</v>
-      </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>1</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67" s="11">
-        <v>0.69971700000000003</v>
-      </c>
+      <c r="E67" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67" s="19">
+        <v>10</v>
+      </c>
+      <c r="G67" s="19">
+        <v>0</v>
+      </c>
+      <c r="H67" s="19"/>
+      <c r="I67" s="19">
+        <v>0</v>
+      </c>
+      <c r="J67" s="19">
+        <v>1</v>
+      </c>
+      <c r="K67" s="19">
+        <v>0</v>
+      </c>
+      <c r="L67" s="2">
+        <v>0.39334799999999998</v>
+      </c>
+      <c r="M67" s="19"/>
       <c r="N67" s="3">
         <v>39</v>
       </c>
@@ -3876,44 +3887,47 @@
       <c r="P67" s="4">
         <v>0</v>
       </c>
-      <c r="Q67">
-        <v>8</v>
-      </c>
-      <c r="R67" s="9">
-        <v>12014</v>
+      <c r="Q67" s="19">
+        <v>7</v>
+      </c>
+      <c r="R67" s="5">
+        <v>8856</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="s">
+      <c r="A68" s="19" t="s">
         <v>83</v>
       </c>
       <c r="B68" s="1">
-        <v>45989</v>
-      </c>
-      <c r="D68" t="s">
+        <v>46002</v>
+      </c>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E68" t="s">
-        <v>17</v>
-      </c>
-      <c r="F68">
-        <v>10</v>
-      </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>1</v>
-      </c>
-      <c r="J68">
-        <v>1</v>
-      </c>
-      <c r="K68">
-        <v>1</v>
-      </c>
-      <c r="L68" s="22">
-        <v>5.7785570000000002</v>
-      </c>
+      <c r="E68" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68" s="19">
+        <v>10</v>
+      </c>
+      <c r="G68" s="19">
+        <v>0</v>
+      </c>
+      <c r="H68" s="19"/>
+      <c r="I68" s="19">
+        <v>1</v>
+      </c>
+      <c r="J68" s="19">
+        <v>1</v>
+      </c>
+      <c r="K68" s="19">
+        <v>1</v>
+      </c>
+      <c r="L68" s="11">
+        <v>3.9288530000000002</v>
+      </c>
+      <c r="M68" s="19"/>
       <c r="N68" s="7">
         <v>39</v>
       </c>
@@ -3923,489 +3937,526 @@
       <c r="P68" s="4">
         <v>0</v>
       </c>
-      <c r="Q68">
+      <c r="Q68" s="19">
         <v>8</v>
       </c>
       <c r="R68" s="5">
-        <v>8713</v>
+        <v>8891</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="s">
+      <c r="A69" s="19" t="s">
         <v>84</v>
       </c>
       <c r="B69" s="1">
-        <v>45989</v>
-      </c>
-      <c r="D69" t="s">
+        <v>46002</v>
+      </c>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E69" t="s">
-        <v>17</v>
-      </c>
-      <c r="F69">
+      <c r="E69" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69" s="19">
         <v>15</v>
       </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>1</v>
-      </c>
-      <c r="K69">
-        <v>0</v>
-      </c>
-      <c r="L69" s="7">
-        <v>32.150188999999997</v>
-      </c>
+      <c r="G69" s="19">
+        <v>0</v>
+      </c>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19">
+        <v>0</v>
+      </c>
+      <c r="J69" s="19">
+        <v>1</v>
+      </c>
+      <c r="K69" s="19">
+        <v>0</v>
+      </c>
+      <c r="L69" s="8">
+        <v>121.477063</v>
+      </c>
+      <c r="M69" s="19"/>
       <c r="N69" s="3">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O69" s="3">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="P69" s="4">
         <v>0</v>
       </c>
-      <c r="Q69">
-        <v>10</v>
-      </c>
-      <c r="R69" s="9">
-        <v>33906</v>
+      <c r="Q69" s="19">
+        <v>9</v>
+      </c>
+      <c r="R69" s="12">
+        <v>449129</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="s">
+      <c r="A70" s="19" t="s">
         <v>85</v>
       </c>
       <c r="B70" s="1">
-        <v>45989</v>
-      </c>
-      <c r="D70" t="s">
+        <v>46002</v>
+      </c>
+      <c r="C70" s="19"/>
+      <c r="D70" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E70" t="s">
-        <v>17</v>
-      </c>
-      <c r="F70">
+      <c r="E70" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F70" s="19">
         <v>15</v>
       </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>1</v>
-      </c>
-      <c r="J70">
-        <v>1</v>
-      </c>
-      <c r="K70">
-        <v>1</v>
-      </c>
-      <c r="L70" s="7">
-        <v>80.973882000000003</v>
-      </c>
-      <c r="N70" s="16">
-        <v>48</v>
-      </c>
-      <c r="O70" s="16">
-        <v>48</v>
+      <c r="G70" s="19">
+        <v>0</v>
+      </c>
+      <c r="H70" s="19"/>
+      <c r="I70" s="19">
+        <v>1</v>
+      </c>
+      <c r="J70" s="19">
+        <v>1</v>
+      </c>
+      <c r="K70" s="19">
+        <v>1</v>
+      </c>
+      <c r="L70" s="8">
+        <v>248.186241</v>
+      </c>
+      <c r="M70" s="19"/>
+      <c r="N70" s="3">
+        <v>45</v>
+      </c>
+      <c r="O70" s="3">
+        <v>45</v>
       </c>
       <c r="P70" s="4">
         <v>0</v>
       </c>
-      <c r="Q70">
-        <v>10</v>
-      </c>
-      <c r="R70" s="5">
-        <v>9168</v>
+      <c r="Q70" s="19">
+        <v>10</v>
+      </c>
+      <c r="R70" s="9">
+        <v>79724</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="s">
+      <c r="A71" s="19" t="s">
         <v>86</v>
       </c>
       <c r="B71" s="1">
-        <v>45989</v>
-      </c>
-      <c r="D71" t="s">
+        <v>46002</v>
+      </c>
+      <c r="C71" s="19"/>
+      <c r="D71" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E71" t="s">
-        <v>17</v>
-      </c>
-      <c r="F71">
+      <c r="E71" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71" s="19">
         <v>20</v>
       </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>1</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="L71" s="10">
-        <v>3600.017069</v>
-      </c>
+      <c r="G71" s="19">
+        <v>0</v>
+      </c>
+      <c r="H71" s="19"/>
+      <c r="I71" s="19">
+        <v>0</v>
+      </c>
+      <c r="J71" s="19">
+        <v>1</v>
+      </c>
+      <c r="K71" s="19">
+        <v>0</v>
+      </c>
+      <c r="L71" s="14">
+        <v>3600.016212</v>
+      </c>
+      <c r="M71" s="19"/>
       <c r="N71" s="3">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="O71" s="3">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="P71" s="2">
-        <v>0.29411799999999999</v>
-      </c>
-      <c r="Q71">
-        <v>10</v>
-      </c>
-      <c r="R71" s="12">
-        <v>793924</v>
+        <v>0.32051299999999999</v>
+      </c>
+      <c r="Q71" s="19">
+        <v>10</v>
+      </c>
+      <c r="R71" s="20">
+        <v>3152730</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="s">
+      <c r="A72" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="B72" s="1">
-        <v>45989</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="B72" s="21">
+        <v>46002</v>
+      </c>
+      <c r="C72" s="19"/>
+      <c r="D72" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E72" t="s">
-        <v>17</v>
-      </c>
-      <c r="F72">
+      <c r="E72" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" s="19">
         <v>20</v>
       </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
-      <c r="I72">
-        <v>1</v>
-      </c>
-      <c r="J72">
-        <v>1</v>
-      </c>
-      <c r="K72">
+      <c r="G72" s="19">
+        <v>0</v>
+      </c>
+      <c r="H72" s="19"/>
+      <c r="I72" s="19">
+        <v>1</v>
+      </c>
+      <c r="J72" s="19">
+        <v>1</v>
+      </c>
+      <c r="K72" s="19">
         <v>1</v>
       </c>
       <c r="L72" s="14">
-        <v>3600.0544460000001</v>
-      </c>
+        <v>3600.0265570000001</v>
+      </c>
+      <c r="M72" s="19"/>
       <c r="N72" s="7">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="O72" s="3">
-        <v>59</v>
-      </c>
-      <c r="P72" s="2">
-        <v>0.289157</v>
-      </c>
-      <c r="Q72">
+        <v>50</v>
+      </c>
+      <c r="P72" s="11">
+        <v>0.34210499999999999</v>
+      </c>
+      <c r="Q72" s="19">
         <v>10</v>
       </c>
       <c r="R72" s="12">
-        <v>165995</v>
+        <v>415951</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="s">
+      <c r="A73" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B73" s="1">
-        <v>45989</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="B73" s="21">
+        <v>46002</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E73" t="s">
-        <v>17</v>
-      </c>
-      <c r="F73">
+      <c r="E73" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F73" s="19">
         <v>25</v>
       </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
-      <c r="I73">
-        <v>0</v>
-      </c>
-      <c r="J73">
-        <v>1</v>
-      </c>
-      <c r="K73">
-        <v>0</v>
-      </c>
-      <c r="L73" s="14">
-        <v>3600.0181240000002</v>
-      </c>
+      <c r="G73" s="19">
+        <v>0</v>
+      </c>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19">
+        <v>0</v>
+      </c>
+      <c r="J73" s="19">
+        <v>1</v>
+      </c>
+      <c r="K73" s="19">
+        <v>0</v>
+      </c>
+      <c r="L73" s="10">
+        <v>3600.0145630000002</v>
+      </c>
+      <c r="M73" s="19"/>
       <c r="N73" s="3">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="O73" s="3">
-        <v>43</v>
-      </c>
-      <c r="P73" s="2">
-        <v>0.44155800000000001</v>
-      </c>
-      <c r="Q73">
-        <v>10</v>
-      </c>
-      <c r="R73" s="12">
-        <v>695473</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
+        <v>36</v>
+      </c>
+      <c r="P73" s="11">
+        <v>0.47826099999999999</v>
+      </c>
+      <c r="Q73" s="19">
+        <v>10</v>
+      </c>
+      <c r="R73" s="20">
+        <v>2505409</v>
+      </c>
+    </row>
+    <row r="74" ht="14.25">
+      <c r="A74" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="B74" s="1">
-        <v>45989</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="B74" s="21">
+        <v>46002</v>
+      </c>
+      <c r="C74" s="19"/>
+      <c r="D74" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E74" t="s">
-        <v>17</v>
-      </c>
-      <c r="F74">
+      <c r="E74" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74" s="19">
         <v>25</v>
       </c>
-      <c r="G74">
-        <v>0</v>
-      </c>
-      <c r="I74">
-        <v>1</v>
-      </c>
-      <c r="J74">
-        <v>1</v>
-      </c>
-      <c r="K74">
+      <c r="G74" s="19">
+        <v>0</v>
+      </c>
+      <c r="H74" s="19"/>
+      <c r="I74" s="19">
+        <v>1</v>
+      </c>
+      <c r="J74" s="19">
+        <v>1</v>
+      </c>
+      <c r="K74" s="19">
         <v>1</v>
       </c>
       <c r="L74" s="14">
-        <v>3600.0452319999999</v>
-      </c>
+        <v>3600.0934419999999</v>
+      </c>
+      <c r="M74" s="19"/>
       <c r="N74" s="7">
-        <v>73</v>
-      </c>
-      <c r="O74" s="7">
+        <v>70</v>
+      </c>
+      <c r="O74" s="3">
         <v>34</v>
       </c>
       <c r="P74" s="11">
-        <v>0.53424700000000003</v>
-      </c>
-      <c r="Q74">
-        <v>10</v>
-      </c>
-      <c r="R74" s="9">
-        <v>23944</v>
+        <v>0.51428600000000002</v>
+      </c>
+      <c r="Q74" s="19">
+        <v>10</v>
+      </c>
+      <c r="R74" s="12">
+        <v>334639</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="s">
+      <c r="A75" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="B75" s="1">
-        <v>45989</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="B75" s="21">
+        <v>46002</v>
+      </c>
+      <c r="C75" s="19"/>
+      <c r="D75" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E75" t="s">
-        <v>17</v>
-      </c>
-      <c r="F75">
+      <c r="E75" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F75" s="19">
         <v>35</v>
       </c>
-      <c r="G75">
-        <v>0</v>
-      </c>
-      <c r="I75">
-        <v>0</v>
-      </c>
-      <c r="J75">
-        <v>1</v>
-      </c>
-      <c r="K75">
-        <v>0</v>
-      </c>
-      <c r="L75" s="10">
-        <v>3600.0431330000001</v>
-      </c>
-      <c r="N75" s="15">
-        <v>102</v>
+      <c r="G75" s="19">
+        <v>0</v>
+      </c>
+      <c r="H75" s="19"/>
+      <c r="I75" s="19">
+        <v>0</v>
+      </c>
+      <c r="J75" s="19">
+        <v>1</v>
+      </c>
+      <c r="K75" s="19">
+        <v>0</v>
+      </c>
+      <c r="L75" s="14">
+        <v>3600.0358769999998</v>
+      </c>
+      <c r="M75" s="19"/>
+      <c r="N75" s="3">
+        <v>94</v>
       </c>
       <c r="O75" s="3">
         <v>48</v>
       </c>
-      <c r="P75" s="11">
-        <v>0.52941199999999999</v>
-      </c>
-      <c r="Q75">
+      <c r="P75" s="2">
+        <v>0.48936200000000002</v>
+      </c>
+      <c r="Q75" s="19">
         <v>10</v>
       </c>
       <c r="R75" s="12">
-        <v>235780</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
+        <v>959261</v>
+      </c>
+    </row>
+    <row r="76" ht="14.25">
+      <c r="A76" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B76" s="1">
-        <v>45989</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="B76" s="21">
+        <v>46002</v>
+      </c>
+      <c r="C76" s="19"/>
+      <c r="D76" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E76" t="s">
-        <v>17</v>
-      </c>
-      <c r="F76">
+      <c r="E76" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F76" s="19">
         <v>35</v>
       </c>
-      <c r="G76">
-        <v>0</v>
-      </c>
-      <c r="I76">
-        <v>1</v>
-      </c>
-      <c r="J76">
-        <v>1</v>
-      </c>
-      <c r="K76">
-        <v>1</v>
-      </c>
-      <c r="L76" s="14">
-        <v>3600.0616279999999</v>
-      </c>
-      <c r="N76" s="15">
-        <v>103</v>
+      <c r="G76" s="19">
+        <v>0</v>
+      </c>
+      <c r="H76" s="19"/>
+      <c r="I76" s="19">
+        <v>1</v>
+      </c>
+      <c r="J76" s="19">
+        <v>1</v>
+      </c>
+      <c r="K76" s="19">
+        <v>1</v>
+      </c>
+      <c r="L76" s="10">
+        <v>3600.04268</v>
+      </c>
+      <c r="M76" s="19"/>
+      <c r="N76" s="7">
+        <v>92</v>
       </c>
       <c r="O76" s="3">
         <v>48</v>
       </c>
       <c r="P76" s="11">
-        <v>0.53398100000000004</v>
-      </c>
-      <c r="Q76">
-        <v>10</v>
-      </c>
-      <c r="R76" s="5">
-        <v>5165</v>
+        <v>0.47826099999999999</v>
+      </c>
+      <c r="Q76" s="19">
+        <v>10</v>
+      </c>
+      <c r="R76" s="9">
+        <v>59647</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="s">
+      <c r="A77" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="B77" s="1">
-        <v>45989</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="B77" s="21">
+        <v>46002</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E77" t="s">
-        <v>17</v>
-      </c>
-      <c r="F77">
+      <c r="E77" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F77" s="19">
         <v>50</v>
       </c>
-      <c r="G77">
-        <v>0</v>
-      </c>
-      <c r="I77">
-        <v>0</v>
-      </c>
-      <c r="J77">
-        <v>1</v>
-      </c>
-      <c r="K77">
-        <v>0</v>
-      </c>
-      <c r="L77" s="14">
-        <v>3600.1104519999999</v>
-      </c>
+      <c r="G77" s="19">
+        <v>0</v>
+      </c>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19">
+        <v>0</v>
+      </c>
+      <c r="J77" s="19">
+        <v>1</v>
+      </c>
+      <c r="K77" s="19">
+        <v>0</v>
+      </c>
+      <c r="L77" s="10">
+        <v>3600.0882729999998</v>
+      </c>
+      <c r="M77" s="19"/>
       <c r="N77" s="15">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="O77" s="3">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="P77" s="11">
-        <v>0.79041899999999998</v>
-      </c>
-      <c r="Q77">
-        <v>10</v>
-      </c>
-      <c r="R77" s="9">
-        <v>23074</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
+        <v>0.69032300000000002</v>
+      </c>
+      <c r="Q77" s="19">
+        <v>10</v>
+      </c>
+      <c r="R77" s="12">
+        <v>218984</v>
+      </c>
+    </row>
+    <row r="78" ht="14.25">
+      <c r="A78" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B78" s="1">
-        <v>45989</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="B78" s="21">
+        <v>46002</v>
+      </c>
+      <c r="C78" s="19"/>
+      <c r="D78" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E78" t="s">
-        <v>17</v>
-      </c>
-      <c r="F78">
+      <c r="E78" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F78" s="19">
         <v>50</v>
       </c>
-      <c r="G78">
-        <v>0</v>
-      </c>
-      <c r="I78">
-        <v>1</v>
-      </c>
-      <c r="J78">
-        <v>1</v>
-      </c>
-      <c r="K78">
+      <c r="G78" s="19">
+        <v>0</v>
+      </c>
+      <c r="H78" s="19"/>
+      <c r="I78" s="19">
+        <v>1</v>
+      </c>
+      <c r="J78" s="19">
+        <v>1</v>
+      </c>
+      <c r="K78" s="19">
         <v>1</v>
       </c>
       <c r="L78" s="14">
-        <v>3600.0452599999999</v>
-      </c>
-      <c r="N78" s="8">
-        <v>178</v>
+        <v>3600.0548939999999</v>
+      </c>
+      <c r="M78" s="19"/>
+      <c r="N78" s="17">
+        <v>150</v>
       </c>
       <c r="O78" s="3">
         <v>35</v>
       </c>
       <c r="P78" s="11">
-        <v>0.80337099999999995</v>
-      </c>
-      <c r="Q78">
-        <v>10</v>
-      </c>
-      <c r="R78" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79"/>
-    <row r="82"/>
-    <row r="86"/>
-    <row r="90"/>
-    <row r="94"/>
-    <row r="98"/>
+        <v>0.76666699999999999</v>
+      </c>
+      <c r="Q78" s="19">
+        <v>10</v>
+      </c>
+      <c r="R78" s="15">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="79" ht="14.25"/>
+    <row r="80" ht="14.25"/>
+    <row r="81"/>
+    <row r="82" ht="14.25"/>
+    <row r="83" ht="14.25"/>
+    <row r="84" ht="14.25"/>
+    <row r="85"/>
+    <row r="86" ht="14.25"/>
+    <row r="87" ht="14.25"/>
+    <row r="88" ht="14.25"/>
+    <row r="89" ht="14.25"/>
+    <row r="90" ht="14.25"/>
+    <row r="91" ht="14.25"/>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
@@ -4422,101 +4473,101 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
     </row>
     <row r="2" ht="14.25">
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="22" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="3" ht="14.25">
-      <c r="C3" s="24" t="str">
+      <c r="C3" s="23" t="str">
         <f>IF(Data!L2&lt;3600,IF(Data!L2&lt;120,TEXT(Data!L2,"0.00")&amp;"s",TEXT(Data!L2,"0")&amp;"s"),TEXT(Data!P2*100,"0")&amp;"%")</f>
         <v>0.29s</v>
       </c>
-      <c r="D3" s="23" t="str">
+      <c r="D3" s="22" t="str">
         <f>IF(Data!L15&lt;3600,IF(Data!L15&lt;120,TEXT(Data!L15,"0.00")&amp;"s",TEXT(Data!L15,"0")&amp;"s"),TEXT(Data!P15*100,"0")&amp;"%")</f>
         <v>1.15s</v>
       </c>
-      <c r="E3" s="23" t="str">
+      <c r="E3" s="22" t="str">
         <f>IF(Data!L28&lt;3600,IF(Data!L28&lt;120,TEXT(Data!L28,"0.00")&amp;"s",TEXT(Data!L28,"0")&amp;"s"),TEXT(Data!P28*100,"0")&amp;"%")</f>
         <v>0.67s</v>
       </c>
-      <c r="F3" s="23" t="str">
+      <c r="F3" s="22" t="str">
         <f>IF(Data!L41&lt;3600,IF(Data!L41&lt;120,TEXT(Data!L41,"0.00")&amp;"s",TEXT(Data!L41,"0")&amp;"s"),TEXT(Data!P41*100,"0")&amp;"%")</f>
         <v>0.66s</v>
       </c>
-      <c r="G3" s="23" t="str">
+      <c r="G3" s="22" t="str">
         <f>IF(Data!L54&lt;3600,IF(Data!L54&lt;120,TEXT(Data!L54,"0.00")&amp;"s",TEXT(Data!L54,"0")&amp;"s"),TEXT(Data!P54*100,"0")&amp;"%")</f>
         <v>0.57s</v>
       </c>
-      <c r="H3" s="23" t="str">
+      <c r="H3" s="22" t="str">
         <f>IF(Data!L67&lt;3600,IF(Data!L67&lt;120,TEXT(Data!L67,"0.00")&amp;"s",TEXT(Data!L67,"0")&amp;"s"),TEXT(Data!P67*100,"0")&amp;"%")</f>
-        <v>0.70s</v>
+        <v>0.39s</v>
       </c>
     </row>
     <row r="4" ht="14.25">
-      <c r="C4" s="23" t="str">
+      <c r="C4" s="22" t="str">
         <f>IF(Data!L3&lt;3600,IF(Data!L3&lt;100,TEXT(Data!L3,"0.00")&amp;"s",TEXT(Data!L3,"0")&amp;"s"),TEXT(Data!P3*100,"0")&amp;"%")</f>
         <v>4.54s</v>
       </c>
-      <c r="D4" s="23" t="str">
+      <c r="D4" s="22" t="str">
         <f>IF(Data!L16&lt;3600,IF(Data!L16&lt;120,TEXT(Data!L16,"0.00")&amp;"s",TEXT(Data!L16,"0")&amp;"s"),TEXT(Data!P16*100,"0")&amp;"%")</f>
         <v>2.24s</v>
       </c>
-      <c r="E4" s="25" t="str">
+      <c r="E4" s="24" t="str">
         <f>IF(Data!L29&lt;3600,IF(Data!L29&lt;120,TEXT(Data!L29,"0.00")&amp;"s",TEXT(Data!L29,"0")&amp;"s"),TEXT(Data!P29*100,"0")&amp;"%")</f>
         <v>6.96s</v>
       </c>
-      <c r="F4" s="23" t="str">
+      <c r="F4" s="22" t="str">
         <f>IF(Data!L42&lt;3600,IF(Data!L42&lt;120,TEXT(Data!L42,"0.00")&amp;"s",TEXT(Data!L42,"0")&amp;"s"),TEXT(Data!P42*100,"0")&amp;"%")</f>
         <v>3.69s</v>
       </c>
-      <c r="G4" s="23" t="str">
+      <c r="G4" s="22" t="str">
         <f>IF(Data!L55&lt;3600,IF(Data!L55&lt;120,TEXT(Data!L55,"0.00")&amp;"s",TEXT(Data!L55,"0")&amp;"s"),TEXT(Data!P55*100,"0")&amp;"%")</f>
         <v>2.68s</v>
       </c>
-      <c r="H4" s="23" t="str">
+      <c r="H4" s="22" t="str">
         <f>IF(Data!L68&lt;3600,IF(Data!L68&lt;120,TEXT(Data!L68,"0.00")&amp;"s",TEXT(Data!L68,"0")&amp;"s"),TEXT(Data!P68*100,"0")&amp;"%")</f>
-        <v>5.78s</v>
+        <v>3.93s</v>
       </c>
     </row>
     <row r="5" ht="14.25">
-      <c r="C5" s="23" t="str">
+      <c r="C5" s="22" t="str">
         <f>IF(Data!L4&lt;3600,IF(Data!L4&lt;100,TEXT(Data!L4,"0.00")&amp;"s",TEXT(Data!L4,"0")&amp;"s"),TEXT(Data!P4*100,"0")&amp;"%")</f>
         <v>102s</v>
       </c>
-      <c r="D5" s="23" t="str">
+      <c r="D5" s="22" t="str">
         <f>IF(Data!L17&lt;3600,IF(Data!L17&lt;120,TEXT(Data!L17,"0.00")&amp;"s",TEXT(Data!L17,"0")&amp;"s"),TEXT(Data!P17*100,"0")&amp;"%")</f>
         <v>237s</v>
       </c>
-      <c r="E5" s="23" t="str">
+      <c r="E5" s="22" t="str">
         <f>IF(Data!L30&lt;3600,IF(Data!L30&lt;120,TEXT(Data!L30,"0.00")&amp;"s",TEXT(Data!L30,"0")&amp;"s"),TEXT(Data!P30*100,"0")&amp;"%")</f>
         <v>61.02s</v>
       </c>
-      <c r="F5" s="23" t="str">
+      <c r="F5" s="22" t="str">
         <f>IF(Data!L43&lt;3600,IF(Data!L43&lt;120,TEXT(Data!L43,"0.00")&amp;"s",TEXT(Data!L43,"0")&amp;"s"),TEXT(Data!P43*100,"0")&amp;"%")</f>
         <v>167s</v>
       </c>
@@ -4524,139 +4575,139 @@
         <f>IF(Data!L56&lt;3600,IF(Data!L56&lt;120,TEXT(Data!L56,"0.00")&amp;"s",TEXT(Data!L56,"0")&amp;"s"),TEXT(Data!P56*100,"0")&amp;"%")</f>
         <v>54.30s</v>
       </c>
-      <c r="H5" s="24" t="str">
+      <c r="H5" s="22" t="str">
         <f>IF(Data!L69&lt;3600,IF(Data!L69&lt;120,TEXT(Data!L69,"0.00")&amp;"s",TEXT(Data!L69,"0")&amp;"s"),TEXT(Data!P69*100,"0")&amp;"%")</f>
-        <v>32.15s</v>
+        <v>121s</v>
       </c>
     </row>
     <row r="6" ht="14.25">
-      <c r="C6" s="23" t="str">
+      <c r="C6" s="22" t="str">
         <f>IF(Data!L5&lt;3600,IF(Data!L5&lt;120,TEXT(Data!L5,"0.00")&amp;"s",TEXT(Data!L5,"0")&amp;"s"),TEXT(Data!P5*100,"0")&amp;"%")</f>
         <v>304s</v>
       </c>
-      <c r="D6" s="25" t="str">
+      <c r="D6" s="24" t="str">
         <f>IF(Data!L18&lt;3600,IF(Data!L18&lt;120,TEXT(Data!L18,"0.00")&amp;"s",TEXT(Data!L18,"0")&amp;"s"),TEXT(Data!P18*100,"0")&amp;"%")</f>
         <v>739s</v>
       </c>
-      <c r="E6" s="23" t="str">
+      <c r="E6" s="22" t="str">
         <f>IF(Data!L31&lt;3600,IF(Data!L31&lt;120,TEXT(Data!L31,"0.00")&amp;"s",TEXT(Data!L31,"0")&amp;"s"),TEXT(Data!P31*100,"0")&amp;"%")</f>
         <v>356s</v>
       </c>
-      <c r="F6" s="23" t="str">
+      <c r="F6" s="22" t="str">
         <f>IF(Data!L44&lt;3600,IF(Data!L44&lt;120,TEXT(Data!L44,"0.00")&amp;"s",TEXT(Data!L44,"0")&amp;"s"),TEXT(Data!P44*100,"0")&amp;"%")</f>
         <v>295s</v>
       </c>
-      <c r="G6" s="23" t="str">
+      <c r="G6" s="22" t="str">
         <f>IF(Data!L57&lt;3600,IF(Data!L57&lt;120,TEXT(Data!L57,"0.00")&amp;"s",TEXT(Data!L57,"0")&amp;"s"),TEXT(Data!P57*100,"0")&amp;"%")</f>
         <v>155s</v>
       </c>
-      <c r="H6" s="23" t="str">
+      <c r="H6" s="22" t="str">
         <f>IF(Data!L70&lt;3600,IF(Data!L70&lt;120,TEXT(Data!L70,"0.00")&amp;"s",TEXT(Data!L70,"0")&amp;"s"),TEXT(Data!P70*100,"0")&amp;"%")</f>
-        <v>80.97s</v>
+        <v>248s</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="C7" s="23" t="str">
+      <c r="C7" s="22" t="str">
         <f>IF(Data!L6&lt;3600,IF(Data!L6&lt;120,TEXT(Data!L6,"0.00")&amp;"s",TEXT(Data!L6,"0")&amp;"s"),TEXT(Data!P6*100,"0")&amp;"%")</f>
         <v>34%</v>
       </c>
-      <c r="D7" s="23" t="str">
+      <c r="D7" s="22" t="str">
         <f>IF(Data!L19&lt;3600,IF(Data!L19&lt;120,TEXT(Data!L19,"0.00")&amp;"s",TEXT(Data!L19,"0")&amp;"s"),TEXT(Data!P19*100,"0")&amp;"%")</f>
         <v>36%</v>
       </c>
-      <c r="E7" s="23" t="str">
+      <c r="E7" s="22" t="str">
         <f>IF(Data!L32&lt;3600,IF(Data!L32&lt;120,TEXT(Data!L32,"0.00")&amp;"s",TEXT(Data!L32,"0")&amp;"s"),TEXT(Data!P32*100,"0")&amp;"%")</f>
         <v>38%</v>
       </c>
-      <c r="F7" s="25" t="str">
+      <c r="F7" s="24" t="str">
         <f>IF(Data!L45&lt;3600,IF(Data!L45&lt;120,TEXT(Data!L45,"0.00")&amp;"s",TEXT(Data!L45,"0")&amp;"s"),TEXT(Data!P45*100,"0")&amp;"%")</f>
         <v>41%</v>
       </c>
-      <c r="G7" s="24" t="str">
+      <c r="G7" s="23" t="str">
         <f>IF(Data!L58&lt;3600,IF(Data!L58&lt;120,TEXT(Data!L58,"0.00")&amp;"s",TEXT(Data!L58,"0")&amp;"s"),TEXT(Data!P58*100,"0")&amp;"%")</f>
         <v>31%</v>
       </c>
-      <c r="H7" s="23" t="str">
+      <c r="H7" s="22" t="str">
         <f>IF(Data!L71&lt;3600,IF(Data!L71&lt;120,TEXT(Data!L71,"0.00")&amp;"s",TEXT(Data!L71,"0")&amp;"s"),TEXT(Data!P71*100,"0")&amp;"%")</f>
-        <v>29%</v>
+        <v>32%</v>
       </c>
     </row>
     <row r="8" ht="14.25">
-      <c r="C8" s="23" t="str">
+      <c r="C8" s="22" t="str">
         <f>IF(Data!L7&lt;3600,IF(Data!L7&lt;120,TEXT(Data!L7,"0.00")&amp;"s",TEXT(Data!L7,"0")&amp;"s"),TEXT(Data!P7*100,"0")&amp;"%")</f>
         <v>38%</v>
       </c>
-      <c r="D8" s="23" t="str">
+      <c r="D8" s="22" t="str">
         <f>IF(Data!L20&lt;3600,IF(Data!L20&lt;120,TEXT(Data!L20,"0.00")&amp;"s",TEXT(Data!L20,"0")&amp;"s"),TEXT(Data!P20*100,"0")&amp;"%")</f>
         <v>40%</v>
       </c>
-      <c r="E8" s="23" t="str">
+      <c r="E8" s="22" t="str">
         <f>IF(Data!L33&lt;3600,IF(Data!L33&lt;120,TEXT(Data!L33,"0.00")&amp;"s",TEXT(Data!L33,"0")&amp;"s"),TEXT(Data!P33*100,"0")&amp;"%")</f>
         <v>40%</v>
       </c>
-      <c r="F8" s="23" t="str">
+      <c r="F8" s="22" t="str">
         <f>IF(Data!L46&lt;3600,IF(Data!L46&lt;120,TEXT(Data!L46,"0.00")&amp;"s",TEXT(Data!L46,"0")&amp;"s"),TEXT(Data!P46*100,"0")&amp;"%")</f>
         <v>39%</v>
       </c>
-      <c r="G8" s="23" t="str">
+      <c r="G8" s="22" t="str">
         <f>IF(Data!L59&lt;3600,IF(Data!L59&lt;120,TEXT(Data!L59,"0.00")&amp;"s",TEXT(Data!L59,"0")&amp;"s"),TEXT(Data!P59*100,"0")&amp;"%")</f>
         <v>35%</v>
       </c>
-      <c r="H8" s="23" t="str">
+      <c r="H8" s="22" t="str">
         <f>IF(Data!L72&lt;3600,IF(Data!L72&lt;120,TEXT(Data!L72,"0.00")&amp;"s",TEXT(Data!L72,"0")&amp;"s"),TEXT(Data!P72*100,"0")&amp;"%")</f>
-        <v>29%</v>
+        <v>34%</v>
       </c>
     </row>
     <row r="9" ht="14.25">
-      <c r="C9" s="23" t="str">
+      <c r="C9" s="22" t="str">
         <f>IF(Data!L8&lt;3600,IF(Data!L8&lt;120,TEXT(Data!L8,"0.00")&amp;"s",TEXT(Data!L8,"0")&amp;"s"),TEXT(Data!P8*100,"0")&amp;"%")</f>
         <v>51%</v>
       </c>
-      <c r="D9" s="23" t="str">
+      <c r="D9" s="22" t="str">
         <f>IF(Data!L21&lt;3600,IF(Data!L21&lt;120,TEXT(Data!L21,"0.00")&amp;"s",TEXT(Data!L21,"0")&amp;"s"),TEXT(Data!P21*100,"0")&amp;"%")</f>
         <v>51%</v>
       </c>
-      <c r="E9" s="23" t="str">
+      <c r="E9" s="24" t="str">
         <f>IF(Data!L34&lt;3600,IF(Data!L34&lt;120,TEXT(Data!L34,"0.00")&amp;"s",TEXT(Data!L34,"0")&amp;"s"),TEXT(Data!P34*100,"0")&amp;"%")</f>
         <v>53%</v>
       </c>
-      <c r="F9" s="23" t="str">
+      <c r="F9" s="22" t="str">
         <f>IF(Data!L47&lt;3600,IF(Data!L47&lt;120,TEXT(Data!L47,"0.00")&amp;"s",TEXT(Data!L47,"0")&amp;"s"),TEXT(Data!P47*100,"0")&amp;"%")</f>
         <v>52%</v>
       </c>
-      <c r="G9" s="24" t="str">
+      <c r="G9" s="22" t="str">
         <f>IF(Data!L60&lt;3600,IF(Data!L60&lt;120,TEXT(Data!L60,"0.00")&amp;"s",TEXT(Data!L60,"0")&amp;"s"),TEXT(Data!P60*100,"0")&amp;"%")</f>
         <v>49%</v>
       </c>
       <c r="H9" s="23" t="str">
         <f>IF(Data!L73&lt;3600,IF(Data!L73&lt;120,TEXT(Data!L73,"0.00")&amp;"s",TEXT(Data!L73,"0")&amp;"s"),TEXT(Data!P73*100,"0")&amp;"%")</f>
-        <v>44%</v>
+        <v>48%</v>
       </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="C10" s="23" t="str">
+      <c r="C10" s="22" t="str">
         <f>IF(Data!L9&lt;3600,IF(Data!L9&lt;120,TEXT(Data!L9,"0.00")&amp;"s",TEXT(Data!L9,"0")&amp;"s"),TEXT(Data!P9*100,"0")&amp;"%")</f>
         <v>51%</v>
       </c>
-      <c r="D10" s="23" t="str">
+      <c r="D10" s="22" t="str">
         <f>IF(Data!L22&lt;3600,IF(Data!L22&lt;120,TEXT(Data!L22,"0.00")&amp;"s",TEXT(Data!L22,"0")&amp;"s"),TEXT(Data!P22*100,"0")&amp;"%")</f>
         <v>52%</v>
       </c>
-      <c r="E10" s="23" t="str">
+      <c r="E10" s="24" t="str">
         <f>IF(Data!L35&lt;3600,IF(Data!L35&lt;120,TEXT(Data!L35,"0.00")&amp;"s",TEXT(Data!L35,"0")&amp;"s"),TEXT(Data!P35*100,"0")&amp;"%")</f>
         <v>53%</v>
       </c>
-      <c r="F10" s="23" t="str">
+      <c r="F10" s="22" t="str">
         <f>IF(Data!L48&lt;3600,IF(Data!L48&lt;120,TEXT(Data!L48,"0.00")&amp;"s",TEXT(Data!L48,"0")&amp;"s"),TEXT(Data!P48*100,"0")&amp;"%")</f>
         <v>52%</v>
       </c>
-      <c r="G10" s="25" t="str">
+      <c r="G10" s="22" t="str">
         <f>IF(Data!L61&lt;3600,IF(Data!L61&lt;120,TEXT(Data!L61,"0.00")&amp;"s",TEXT(Data!L61,"0")&amp;"s"),TEXT(Data!P61*100,"0")&amp;"%")</f>
         <v>51%</v>
       </c>
-      <c r="H10" s="23" t="str">
+      <c r="H10" s="22" t="str">
         <f>IF(Data!L74&lt;3600,IF(Data!L74&lt;120,TEXT(Data!L74,"0.00")&amp;"s",TEXT(Data!L74,"0")&amp;"s"),TEXT(Data!P74*100,"0")&amp;"%")</f>
-        <v>53%</v>
+        <v>51%</v>
       </c>
     </row>
     <row r="11" ht="14.25">
@@ -4668,21 +4719,21 @@
         <f>IF(Data!L23&lt;3600,IF(Data!L23&lt;120,TEXT(Data!L23,"0.00")&amp;"s",TEXT(Data!L23,"0")&amp;"s"),TEXT(Data!P23*100,"0")&amp;"%")</f>
         <v>48%</v>
       </c>
-      <c r="E11" s="23" t="str">
+      <c r="E11" s="24" t="str">
         <f>IF(Data!L36&lt;3600,IF(Data!L36&lt;120,TEXT(Data!L36,"0.00")&amp;"s",TEXT(Data!L36,"0")&amp;"s"),TEXT(Data!P36*100,"0")&amp;"%")</f>
         <v>52%</v>
       </c>
-      <c r="F11" s="24" t="str">
+      <c r="F11" s="22" t="str">
         <f>IF(Data!L49&lt;3600,IF(Data!L49&lt;120,TEXT(Data!L49,"0.00")&amp;"s",TEXT(Data!L49,"0")&amp;"s"),TEXT(Data!P49*100,"0")&amp;"%")</f>
         <v>51%</v>
       </c>
-      <c r="G11" s="23" t="str">
+      <c r="G11" s="22" t="str">
         <f>IF(Data!L62&lt;3600,IF(Data!L62&lt;120,TEXT(Data!L62,"0.00")&amp;"s",TEXT(Data!L62,"0")&amp;"s"),TEXT(Data!P62*100,"0")&amp;"%")</f>
         <v>49%</v>
       </c>
-      <c r="H11" s="25" t="str">
+      <c r="H11" s="22" t="str">
         <f>IF(Data!L75&lt;3600,IF(Data!L75&lt;120,TEXT(Data!L75,"0.00")&amp;"s",TEXT(Data!L75,"0")&amp;"s"),TEXT(Data!P75*100,"0")&amp;"%")</f>
-        <v>53%</v>
+        <v>49%</v>
       </c>
     </row>
     <row r="12" ht="14.25">
@@ -4694,73 +4745,73 @@
         <f>IF(Data!L24&lt;3600,IF(Data!L24&lt;120,TEXT(Data!L24,"0.00")&amp;"s",TEXT(Data!L24,"0")&amp;"s"),TEXT(Data!P24*100,"0")&amp;"%")</f>
         <v>48%</v>
       </c>
-      <c r="E12" s="24" t="str">
+      <c r="E12" s="22" t="str">
         <f>IF(Data!L37&lt;3600,IF(Data!L37&lt;120,TEXT(Data!L37,"0.00")&amp;"s",TEXT(Data!L37,"0")&amp;"s"),TEXT(Data!P37*100,"0")&amp;"%")</f>
         <v>51%</v>
       </c>
-      <c r="F12" s="23" t="str">
+      <c r="F12" s="24" t="str">
         <f>IF(Data!L50&lt;3600,IF(Data!L50&lt;120,TEXT(Data!L50,"0.00")&amp;"s",TEXT(Data!L50,"0")&amp;"s"),TEXT(Data!P50*100,"0")&amp;"%")</f>
         <v>52%</v>
       </c>
-      <c r="G12" s="23" t="str">
+      <c r="G12" s="22" t="str">
         <f>IF(Data!L63&lt;3600,IF(Data!L63&lt;120,TEXT(Data!L63,"0.00")&amp;"s",TEXT(Data!L63,"0")&amp;"s"),TEXT(Data!P63*100,"0")&amp;"%")</f>
-        <v>52%</v>
-      </c>
-      <c r="H12" s="25" t="str">
+        <v>49%</v>
+      </c>
+      <c r="H12" s="23" t="str">
         <f>IF(Data!L76&lt;3600,IF(Data!L76&lt;120,TEXT(Data!L76,"0.00")&amp;"s",TEXT(Data!L76,"0")&amp;"s"),TEXT(Data!P76*100,"0")&amp;"%")</f>
-        <v>53%</v>
+        <v>48%</v>
       </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="C13" s="23" t="str">
+      <c r="C13" s="22" t="str">
         <f>IF(Data!L12&lt;3600,IF(Data!L12&lt;120,TEXT(Data!L12,"0.00")&amp;"s",TEXT(Data!L12,"0")&amp;"s"),TEXT(Data!P12*100,"0")&amp;"%")</f>
         <v>81%</v>
       </c>
-      <c r="D13" s="25" t="str">
+      <c r="D13" s="24" t="str">
         <f>IF(Data!L25&lt;3600,IF(Data!L25&lt;120,TEXT(Data!L25,"0.00")&amp;"s",TEXT(Data!L25,"0")&amp;"s"),TEXT(Data!P25*100,"0")&amp;"%")</f>
         <v>82%</v>
       </c>
-      <c r="E13" s="25" t="str">
+      <c r="E13" s="24" t="str">
         <f>IF(Data!L38&lt;3600,IF(Data!L38&lt;120,TEXT(Data!L38,"0.00")&amp;"s",TEXT(Data!L38,"0")&amp;"s"),TEXT(Data!P38*100,"0")&amp;"%")</f>
         <v>82%</v>
       </c>
-      <c r="F13" s="25" t="str">
+      <c r="F13" s="24" t="str">
         <f>IF(Data!L51&lt;3600,IF(Data!L51&lt;120,TEXT(Data!L51,"0.00")&amp;"s",TEXT(Data!L51,"0")&amp;"s"),TEXT(Data!P51*100,"0")&amp;"%")</f>
         <v>82%</v>
       </c>
-      <c r="G13" s="24" t="str">
+      <c r="G13" s="23" t="str">
         <f>IF(Data!L64&lt;3600,IF(Data!L64&lt;120,TEXT(Data!L64,"0.00")&amp;"s",TEXT(Data!L64,"0")&amp;"s"),TEXT(Data!P64*100,"0")&amp;"%")</f>
-        <v>70%</v>
+        <v>69%</v>
       </c>
       <c r="H13" s="23" t="str">
         <f>IF(Data!L77&lt;3600,IF(Data!L77&lt;120,TEXT(Data!L77,"0.00")&amp;"s",TEXT(Data!L77,"0")&amp;"s"),TEXT(Data!P77*100,"0")&amp;"%")</f>
-        <v>79%</v>
+        <v>69%</v>
       </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="C14" s="23" t="str">
+      <c r="C14" s="22" t="str">
         <f>IF(Data!L13&lt;3600,IF(Data!L13&lt;120,TEXT(Data!L13,"0.00")&amp;"s",TEXT(Data!L13,"0")&amp;"s"),TEXT(Data!P13*100,"0")&amp;"%")</f>
         <v>72%</v>
       </c>
-      <c r="D14" s="23" t="str">
+      <c r="D14" s="22" t="str">
         <f>IF(Data!L26&lt;3600,IF(Data!L26&lt;120,TEXT(Data!L26,"0.00")&amp;"s",TEXT(Data!L26,"0")&amp;"s"),TEXT(Data!P26*100,"0")&amp;"%")</f>
         <v>74%</v>
       </c>
-      <c r="E14" s="23" t="str">
+      <c r="E14" s="22" t="str">
         <f>IF(Data!L39&lt;3600,IF(Data!L39&lt;120,TEXT(Data!L39,"0.00")&amp;"s",TEXT(Data!L39,"0")&amp;"s"),TEXT(Data!P39*100,"0")&amp;"%")</f>
         <v>77%</v>
       </c>
-      <c r="F14" s="23" t="str">
+      <c r="F14" s="22" t="str">
         <f>IF(Data!L52&lt;3600,IF(Data!L52&lt;120,TEXT(Data!L52,"0.00")&amp;"s",TEXT(Data!L52,"0")&amp;"s"),TEXT(Data!P52*100,"0")&amp;"%")</f>
         <v>77%</v>
       </c>
-      <c r="G14" s="23" t="str">
+      <c r="G14" s="22" t="str">
         <f>IF(Data!L65&lt;3600,IF(Data!L65&lt;120,TEXT(Data!L65,"0.00")&amp;"s",TEXT(Data!L65,"0")&amp;"s"),TEXT(Data!P65*100,"0")&amp;"%")</f>
-        <v>79%</v>
-      </c>
-      <c r="H14" s="23" t="str">
+        <v>77%</v>
+      </c>
+      <c r="H14" s="22" t="str">
         <f>IF(Data!L78&lt;3600,IF(Data!L78&lt;120,TEXT(Data!L78,"0.00")&amp;"s",TEXT(Data!L78,"0")&amp;"s"),TEXT(Data!P78*100,"0")&amp;"%")</f>
-        <v>80%</v>
+        <v>77%</v>
       </c>
     </row>
     <row r="15" ht="14.25">
@@ -4768,338 +4819,337 @@
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
+      <c r="G15" s="22"/>
       <c r="H15" s="19"/>
     </row>
     <row r="16" ht="14.25">
-      <c r="C16" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
+      <c r="C16" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="H16" s="22"/>
     </row>
     <row r="17" ht="14.25">
-      <c r="C17" s="26">
+      <c r="C17" s="22">
         <f>Data!N2</f>
         <v>39</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="22">
         <f>Data!N15</f>
         <v>39</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="22">
         <f>Data!N28</f>
         <v>39</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="22">
         <f>Data!N41</f>
         <v>39</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="22">
         <f>Data!N54</f>
         <v>39</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="22">
         <f>Data!N67</f>
         <v>39</v>
       </c>
     </row>
     <row r="18" ht="14.25">
-      <c r="C18" s="23">
+      <c r="C18" s="22">
         <f>Data!N3</f>
         <v>39</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="22">
         <f>Data!N16</f>
         <v>39</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="22">
         <f>Data!N29</f>
         <v>39</v>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="22">
         <f>Data!N42</f>
         <v>39</v>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="22">
         <f>Data!N55</f>
         <v>39</v>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="22">
         <f>Data!N68</f>
         <v>39</v>
       </c>
     </row>
     <row r="19" ht="14.25">
-      <c r="C19" s="23">
+      <c r="C19" s="22">
         <f>Data!N4</f>
         <v>45</v>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="22">
         <f>Data!N17</f>
         <v>45</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="22">
         <f>Data!N30</f>
         <v>45</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="22">
         <f>Data!N43</f>
         <v>45</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="22">
         <f>Data!N56</f>
         <v>45</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="22">
         <f>Data!N69</f>
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" ht="14.25">
-      <c r="C20" s="23">
+      <c r="C20" s="22">
         <f>Data!N5</f>
         <v>45</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="22">
         <f>Data!N18</f>
         <v>45</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="22">
         <f>Data!N31</f>
         <v>45</v>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="22">
         <f>Data!N44</f>
         <v>45</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="22">
         <f>Data!N57</f>
         <v>45</v>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="22">
         <f>Data!N70</f>
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" ht="14.25">
-      <c r="C21" s="23">
+      <c r="C21" s="22">
         <f>Data!N6</f>
         <v>76</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="22">
         <f>Data!N19</f>
         <v>78</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="22">
         <f>Data!N32</f>
         <v>78</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="22">
         <f>Data!N45</f>
         <v>78</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="22">
         <f>Data!N58</f>
         <v>77</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="22">
         <f>Data!N71</f>
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" ht="14.25">
-      <c r="C22" s="23">
+      <c r="C22" s="22">
         <f>Data!N7</f>
         <v>77</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="22">
         <f>Data!N20</f>
         <v>80</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="22">
         <f>Data!N33</f>
         <v>80</v>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="22">
         <f>Data!N46</f>
         <v>79</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="22">
         <f>Data!N59</f>
         <v>77</v>
       </c>
-      <c r="H22" s="23">
+      <c r="H22" s="22">
         <f>Data!N72</f>
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" ht="14.25">
-      <c r="C23" s="23">
+      <c r="C23" s="22">
         <f>Data!N8</f>
         <v>70</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="22">
         <f>Data!N21</f>
         <v>69</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="22">
         <f>Data!N34</f>
         <v>72</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="22">
         <f>Data!N47</f>
         <v>71</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="22">
         <f>Data!N60</f>
         <v>70</v>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="22">
         <f>Data!N73</f>
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" ht="14.25">
-      <c r="C24" s="23">
+      <c r="C24" s="22">
         <f>Data!N9</f>
         <v>70</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="22">
         <f>Data!N22</f>
         <v>71</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="22">
         <f>Data!N35</f>
         <v>73</v>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="22">
         <f>Data!N48</f>
         <v>71</v>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="22">
         <f>Data!N61</f>
         <v>69</v>
       </c>
-      <c r="H24" s="23">
+      <c r="H24" s="22">
         <f>Data!N74</f>
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" ht="14.25">
-      <c r="C25" s="23">
+      <c r="C25" s="22">
         <f>Data!N10</f>
         <v>93</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="22">
         <f>Data!N23</f>
         <v>93</v>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="22">
         <f>Data!N36</f>
         <v>101</v>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="22">
         <f>Data!N49</f>
         <v>98</v>
       </c>
-      <c r="G25" s="23">
+      <c r="G25" s="22">
         <f>Data!N62</f>
         <v>94</v>
       </c>
-      <c r="H25" s="23">
+      <c r="H25" s="22">
         <f>Data!N75</f>
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" ht="14.25">
-      <c r="C26" s="23">
+      <c r="C26" s="22">
         <f>Data!N11</f>
         <v>92</v>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="22">
         <f>Data!N24</f>
         <v>93</v>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="22">
         <f>Data!N37</f>
         <v>97</v>
       </c>
-      <c r="F26" s="23">
+      <c r="F26" s="22">
         <f>Data!N50</f>
         <v>99</v>
       </c>
-      <c r="G26" s="23">
+      <c r="G26" s="22">
         <f>Data!N63</f>
-        <v>99</v>
-      </c>
-      <c r="H26" s="23">
+        <v>94</v>
+      </c>
+      <c r="H26" s="22">
         <f>Data!N76</f>
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" ht="14.25">
-      <c r="C27" s="23">
+      <c r="C27" s="22">
         <f>Data!N12</f>
         <v>180</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="22">
         <f>Data!N25</f>
         <v>191</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="22">
         <f>Data!N38</f>
         <v>191.59999999999999</v>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="22">
         <f>Data!N51</f>
         <v>191.59999999999999</v>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="22">
         <f>Data!N64</f>
-        <v>166</v>
-      </c>
-      <c r="H27" s="23">
+        <v>157</v>
+      </c>
+      <c r="H27" s="22">
         <f>Data!N77</f>
-        <v>167</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" ht="14.25">
-      <c r="C28" s="23">
+      <c r="C28" s="22">
         <f>Data!N13</f>
         <v>145</v>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="22">
         <f>Data!N26</f>
         <v>153</v>
       </c>
-      <c r="E28" s="23">
+      <c r="E28" s="22">
         <f>Data!N39</f>
         <v>171</v>
       </c>
-      <c r="F28" s="23">
+      <c r="F28" s="22">
         <f>Data!N52</f>
         <v>171</v>
       </c>
-      <c r="G28" s="23">
+      <c r="G28" s="22">
         <f>Data!N65</f>
-        <v>167</v>
-      </c>
-      <c r="H28" s="23">
+        <v>153</v>
+      </c>
+      <c r="H28" s="22">
         <f>Data!N78</f>
-        <v>178</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" ht="14.25">
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
     </row>
     <row r="30" ht="14.25">
       <c r="C30" t="s">
@@ -5107,313 +5157,313 @@
       </c>
     </row>
     <row r="31" ht="14.25">
-      <c r="C31" s="27">
+      <c r="C31" s="25">
         <f>Data!O2</f>
         <v>39</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="25">
         <f>Data!O15</f>
         <v>39</v>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="25">
         <f>Data!O28</f>
         <v>39</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="25">
         <f>Data!O41</f>
         <v>39</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="25">
         <f>Data!O54</f>
         <v>39</v>
       </c>
-      <c r="H31" s="27">
+      <c r="H31" s="25">
         <f>Data!O67</f>
         <v>39</v>
       </c>
     </row>
     <row r="32" ht="14.25">
-      <c r="C32" s="27">
+      <c r="C32" s="25">
         <f>Data!O3</f>
         <v>39</v>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="25">
         <f>Data!O16</f>
         <v>39</v>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="25">
         <f>Data!O29</f>
         <v>39</v>
       </c>
-      <c r="F32" s="27">
+      <c r="F32" s="25">
         <f>Data!O42</f>
         <v>39</v>
       </c>
-      <c r="G32" s="27">
+      <c r="G32" s="25">
         <f>Data!O55</f>
         <v>39</v>
       </c>
-      <c r="H32" s="27">
+      <c r="H32" s="25">
         <f>Data!O68</f>
         <v>39</v>
       </c>
     </row>
     <row r="33" ht="14.25">
-      <c r="C33" s="27">
+      <c r="C33" s="25">
         <f>Data!O4</f>
         <v>45</v>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="25">
         <f>Data!O17</f>
         <v>45</v>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="25">
         <f>Data!O30</f>
         <v>45</v>
       </c>
-      <c r="F33" s="27">
+      <c r="F33" s="25">
         <f>Data!O43</f>
         <v>45</v>
       </c>
-      <c r="G33" s="27">
+      <c r="G33" s="25">
         <f>Data!O56</f>
         <v>45</v>
       </c>
-      <c r="H33" s="27">
+      <c r="H33" s="25">
         <f>Data!O69</f>
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" ht="14.25">
-      <c r="C34" s="27">
+      <c r="C34" s="25">
         <f>Data!O5</f>
         <v>45</v>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="25">
         <f>Data!O18</f>
         <v>45</v>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="25">
         <f>Data!O31</f>
         <v>45</v>
       </c>
-      <c r="F34" s="27">
+      <c r="F34" s="25">
         <f>Data!O44</f>
         <v>45</v>
       </c>
-      <c r="G34" s="27">
+      <c r="G34" s="25">
         <f>Data!O57</f>
         <v>45</v>
       </c>
-      <c r="H34" s="27">
+      <c r="H34" s="25">
         <f>Data!O70</f>
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" ht="14.25">
-      <c r="C35" s="23">
+      <c r="C35" s="22">
         <f>Data!O6</f>
         <v>50</v>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="22">
         <f>Data!O19</f>
         <v>50</v>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="22">
         <f>Data!O32</f>
         <v>48</v>
       </c>
-      <c r="F35" s="23">
+      <c r="F35" s="22">
         <f>Data!O45</f>
         <v>46</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="25">
         <f>Data!O58</f>
         <v>53</v>
       </c>
-      <c r="H35" s="23">
+      <c r="H35" s="25">
         <f>Data!O71</f>
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" ht="14.25">
-      <c r="C36" s="23">
+      <c r="C36" s="22">
         <f>Data!O7</f>
         <v>48</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="22">
         <f>Data!O20</f>
         <v>48</v>
       </c>
-      <c r="E36" s="23">
+      <c r="E36" s="22">
         <f>Data!O33</f>
         <v>48</v>
       </c>
-      <c r="F36" s="23">
+      <c r="F36" s="22">
         <f>Data!O46</f>
         <v>48</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="25">
         <f>Data!O59</f>
         <v>50</v>
       </c>
-      <c r="H36" s="23">
+      <c r="H36" s="25">
         <f>Data!O72</f>
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" ht="14.25">
-      <c r="C37" s="23">
+      <c r="C37" s="22">
         <f>Data!O8</f>
         <v>34</v>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="22">
         <f>Data!O21</f>
         <v>34</v>
       </c>
-      <c r="E37" s="23">
+      <c r="E37" s="22">
         <f>Data!O34</f>
         <v>34</v>
       </c>
-      <c r="F37" s="23">
+      <c r="F37" s="22">
         <f>Data!O47</f>
         <v>34</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G37" s="25">
         <f>Data!O60</f>
         <v>36</v>
       </c>
-      <c r="H37" s="23">
+      <c r="H37" s="25">
         <f>Data!O73</f>
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" ht="14.25">
-      <c r="C38" s="23">
+      <c r="C38" s="22">
         <f>Data!O9</f>
         <v>34</v>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="22">
         <f>Data!O22</f>
         <v>34</v>
       </c>
-      <c r="E38" s="23">
+      <c r="E38" s="22">
         <f>Data!O35</f>
         <v>34</v>
       </c>
-      <c r="F38" s="23">
+      <c r="F38" s="22">
         <f>Data!O48</f>
         <v>34</v>
       </c>
-      <c r="G38" s="23">
+      <c r="G38" s="25">
         <f>Data!O61</f>
         <v>34</v>
       </c>
-      <c r="H38" s="23">
+      <c r="H38" s="25">
         <f>Data!O74</f>
         <v>34</v>
       </c>
     </row>
     <row r="39" ht="14.25">
-      <c r="C39" s="23">
+      <c r="C39" s="22">
         <f>Data!O10</f>
         <v>48</v>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="22">
         <f>Data!O23</f>
         <v>48</v>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="22">
         <f>Data!O36</f>
         <v>48</v>
       </c>
-      <c r="F39" s="23">
+      <c r="F39" s="22">
         <f>Data!O49</f>
         <v>48</v>
       </c>
-      <c r="G39" s="23">
+      <c r="G39" s="25">
         <f>Data!O62</f>
         <v>48</v>
       </c>
-      <c r="H39" s="23">
+      <c r="H39" s="25">
         <f>Data!O75</f>
         <v>48</v>
       </c>
     </row>
     <row r="40" ht="14.25">
-      <c r="C40" s="23">
+      <c r="C40" s="22">
         <f>Data!O11</f>
         <v>48</v>
       </c>
-      <c r="D40" s="23">
+      <c r="D40" s="22">
         <f>Data!O24</f>
         <v>48</v>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="22">
         <f>Data!O37</f>
         <v>48</v>
       </c>
-      <c r="F40" s="23">
+      <c r="F40" s="22">
         <f>Data!O50</f>
         <v>48</v>
       </c>
-      <c r="G40" s="23">
+      <c r="G40" s="25">
         <f>Data!O63</f>
         <v>48</v>
       </c>
-      <c r="H40" s="23">
+      <c r="H40" s="25">
         <f>Data!O76</f>
         <v>48</v>
       </c>
     </row>
     <row r="41" ht="14.25">
-      <c r="C41" s="23">
+      <c r="C41" s="22">
         <f>Data!O12</f>
         <v>35</v>
       </c>
-      <c r="D41" s="23">
+      <c r="D41" s="22">
         <f>Data!O25</f>
         <v>35</v>
       </c>
-      <c r="E41" s="23">
+      <c r="E41" s="22">
         <f>Data!O38</f>
         <v>35</v>
       </c>
-      <c r="F41" s="23">
+      <c r="F41" s="22">
         <f>Data!O51</f>
         <v>35</v>
       </c>
-      <c r="G41" s="23">
+      <c r="G41" s="25">
         <f>Data!O64</f>
-        <v>50</v>
-      </c>
-      <c r="H41" s="23">
+        <v>48</v>
+      </c>
+      <c r="H41" s="25">
         <f>Data!O77</f>
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" ht="14.25">
-      <c r="C42" s="23">
+      <c r="C42" s="22">
         <f>Data!O13</f>
         <v>40</v>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="22">
         <f>Data!O26</f>
         <v>40</v>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="22">
         <f>Data!O39</f>
         <v>40</v>
       </c>
-      <c r="F42" s="23">
+      <c r="F42" s="22">
         <f>Data!O52</f>
         <v>40</v>
       </c>
-      <c r="G42" s="23">
+      <c r="G42" s="25">
         <f>Data!O65</f>
         <v>35</v>
       </c>
-      <c r="H42" s="23">
+      <c r="H42" s="25">
         <f>Data!O78</f>
         <v>35</v>
       </c>
@@ -5423,7 +5473,7 @@
       <c r="D43" s="26"/>
       <c r="E43" s="26"/>
       <c r="F43" s="26"/>
-      <c r="G43" s="26"/>
+      <c r="G43" s="25"/>
       <c r="H43" s="26"/>
     </row>
     <row r="44" ht="14.25">
@@ -5432,652 +5482,653 @@
       </c>
     </row>
     <row r="45" ht="14.25">
-      <c r="C45" s="27">
+      <c r="C45" s="25">
         <f>Data!Q2</f>
         <v>7</v>
       </c>
-      <c r="D45" s="27">
+      <c r="D45" s="25">
         <f>Data!Q15</f>
         <v>9</v>
       </c>
-      <c r="E45" s="27">
+      <c r="E45" s="25">
         <f>Data!Q28</f>
         <v>7</v>
       </c>
-      <c r="F45" s="27">
+      <c r="F45" s="25">
         <f>Data!Q41</f>
         <v>7</v>
       </c>
-      <c r="G45" s="27">
+      <c r="G45" s="25">
         <f>Data!Q54</f>
         <v>7</v>
       </c>
-      <c r="H45" s="27">
+      <c r="H45" s="25">
         <f>Data!Q67</f>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" ht="14.25">
-      <c r="C46" s="27">
+      <c r="C46" s="25">
         <f>Data!Q3</f>
         <v>8</v>
       </c>
-      <c r="D46" s="27">
+      <c r="D46" s="25">
         <f>Data!Q16</f>
         <v>9</v>
       </c>
-      <c r="E46" s="27">
+      <c r="E46" s="25">
         <f>Data!Q29</f>
         <v>10</v>
       </c>
-      <c r="F46" s="27">
+      <c r="F46" s="25">
         <f>Data!Q42</f>
         <v>9</v>
       </c>
-      <c r="G46" s="27">
+      <c r="G46" s="25">
         <f>Data!Q55</f>
         <v>6</v>
       </c>
-      <c r="H46" s="27">
+      <c r="H46" s="25">
         <f>Data!Q68</f>
         <v>8</v>
       </c>
     </row>
     <row r="47" ht="14.25">
-      <c r="C47" s="27">
+      <c r="C47" s="25">
         <f>Data!Q4</f>
         <v>10</v>
       </c>
-      <c r="D47" s="27">
+      <c r="D47" s="25">
         <f>Data!Q17</f>
         <v>10</v>
       </c>
-      <c r="E47" s="27">
+      <c r="E47" s="25">
         <f>Data!Q30</f>
         <v>10</v>
       </c>
-      <c r="F47" s="27">
+      <c r="F47" s="25">
         <f>Data!Q43</f>
         <v>10</v>
       </c>
-      <c r="G47" s="27">
+      <c r="G47" s="25">
         <f>Data!Q56</f>
         <v>10</v>
       </c>
-      <c r="H47" s="27">
+      <c r="H47" s="25">
         <f>Data!Q69</f>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" ht="14.25">
-      <c r="C48" s="27">
+      <c r="C48" s="25">
         <f>Data!Q5</f>
         <v>10</v>
       </c>
-      <c r="D48" s="27">
+      <c r="D48" s="25">
         <f>Data!Q18</f>
         <v>10</v>
       </c>
-      <c r="E48" s="27">
+      <c r="E48" s="25">
         <f>Data!Q31</f>
         <v>10</v>
       </c>
-      <c r="F48" s="27">
+      <c r="F48" s="25">
         <f>Data!Q44</f>
         <v>10</v>
       </c>
-      <c r="G48" s="27">
+      <c r="G48" s="25">
         <f>Data!Q57</f>
         <v>10</v>
       </c>
-      <c r="H48" s="27">
+      <c r="H48" s="25">
         <f>Data!Q70</f>
         <v>10</v>
       </c>
     </row>
     <row r="49" ht="14.25">
-      <c r="C49" s="27">
+      <c r="C49" s="25">
         <f>Data!Q6</f>
         <v>10</v>
       </c>
-      <c r="D49" s="27">
+      <c r="D49" s="25">
         <f>Data!Q19</f>
         <v>10</v>
       </c>
-      <c r="E49" s="27">
+      <c r="E49" s="25">
         <f>Data!Q32</f>
         <v>10</v>
       </c>
-      <c r="F49" s="27">
+      <c r="F49" s="25">
         <f>Data!Q45</f>
         <v>10</v>
       </c>
-      <c r="G49" s="27">
+      <c r="G49" s="25">
         <f>Data!Q58</f>
         <v>10</v>
       </c>
-      <c r="H49" s="27">
+      <c r="H49" s="25">
         <f>Data!Q71</f>
         <v>10</v>
       </c>
     </row>
     <row r="50" ht="14.25">
-      <c r="C50" s="27">
+      <c r="C50" s="25">
         <f>Data!Q7</f>
         <v>10</v>
       </c>
-      <c r="D50" s="27">
+      <c r="D50" s="25">
         <f>Data!Q20</f>
         <v>10</v>
       </c>
-      <c r="E50" s="27">
+      <c r="E50" s="25">
         <f>Data!Q33</f>
         <v>10</v>
       </c>
-      <c r="F50" s="27">
+      <c r="F50" s="25">
         <f>Data!Q46</f>
         <v>10</v>
       </c>
-      <c r="G50" s="27">
+      <c r="G50" s="25">
         <f>Data!Q59</f>
         <v>10</v>
       </c>
-      <c r="H50" s="27">
+      <c r="H50" s="25">
         <f>Data!Q72</f>
         <v>10</v>
       </c>
     </row>
     <row r="51" ht="14.25">
-      <c r="C51" s="27">
+      <c r="C51" s="25">
         <f>Data!Q8</f>
         <v>10</v>
       </c>
-      <c r="D51" s="27">
+      <c r="D51" s="25">
         <f>Data!Q21</f>
         <v>10</v>
       </c>
-      <c r="E51" s="27">
+      <c r="E51" s="25">
         <f>Data!Q34</f>
         <v>10</v>
       </c>
-      <c r="F51" s="27">
+      <c r="F51" s="25">
         <f>Data!Q47</f>
         <v>10</v>
       </c>
-      <c r="G51" s="27">
+      <c r="G51" s="25">
         <f>Data!Q60</f>
         <v>10</v>
       </c>
-      <c r="H51" s="27">
+      <c r="H51" s="25">
         <f>Data!Q73</f>
         <v>10</v>
       </c>
     </row>
     <row r="52" ht="14.25">
-      <c r="C52" s="27">
+      <c r="C52" s="25">
         <f>Data!Q9</f>
         <v>10</v>
       </c>
-      <c r="D52" s="27">
+      <c r="D52" s="25">
         <f>Data!Q22</f>
         <v>10</v>
       </c>
-      <c r="E52" s="27">
+      <c r="E52" s="25">
         <f>Data!Q35</f>
         <v>10</v>
       </c>
-      <c r="F52" s="27">
+      <c r="F52" s="25">
         <f>Data!Q48</f>
         <v>10</v>
       </c>
-      <c r="G52" s="27">
+      <c r="G52" s="25">
         <f>Data!Q61</f>
         <v>10</v>
       </c>
-      <c r="H52" s="27">
+      <c r="H52" s="25">
         <f>Data!Q74</f>
         <v>10</v>
       </c>
     </row>
     <row r="53" ht="14.25">
-      <c r="C53" s="27">
+      <c r="C53" s="25">
         <f>Data!Q10</f>
         <v>10</v>
       </c>
-      <c r="D53" s="27">
+      <c r="D53" s="25">
         <f>Data!Q23</f>
         <v>10</v>
       </c>
-      <c r="E53" s="27">
+      <c r="E53" s="25">
         <f>Data!Q36</f>
         <v>10</v>
       </c>
-      <c r="F53" s="27">
+      <c r="F53" s="25">
         <f>Data!Q49</f>
         <v>10</v>
       </c>
-      <c r="G53" s="27">
+      <c r="G53" s="25">
         <f>Data!Q62</f>
         <v>10</v>
       </c>
-      <c r="H53" s="27">
+      <c r="H53" s="25">
         <f>Data!Q75</f>
         <v>10</v>
       </c>
     </row>
     <row r="54" ht="14.25">
-      <c r="C54" s="27">
+      <c r="C54" s="25">
         <f>Data!Q11</f>
         <v>10</v>
       </c>
-      <c r="D54" s="27">
+      <c r="D54" s="25">
         <f>Data!Q24</f>
         <v>10</v>
       </c>
-      <c r="E54" s="27">
+      <c r="E54" s="25">
         <f>Data!Q37</f>
         <v>10</v>
       </c>
-      <c r="F54" s="27">
+      <c r="F54" s="25">
         <f>Data!Q50</f>
         <v>10</v>
       </c>
-      <c r="G54" s="27">
+      <c r="G54" s="25">
         <f>Data!Q63</f>
         <v>10</v>
       </c>
-      <c r="H54" s="27">
+      <c r="H54" s="25">
         <f>Data!Q76</f>
         <v>10</v>
       </c>
     </row>
     <row r="55" ht="14.25">
-      <c r="C55" s="27">
+      <c r="C55" s="25">
         <f>Data!Q12</f>
         <v>5</v>
       </c>
-      <c r="D55" s="27">
+      <c r="D55" s="25">
         <f>Data!Q25</f>
         <v>2</v>
       </c>
-      <c r="E55" s="28">
+      <c r="E55" s="27">
         <f>Data!Q38</f>
         <v>1</v>
       </c>
-      <c r="F55" s="28">
+      <c r="F55" s="27">
         <f>Data!Q51</f>
         <v>1</v>
       </c>
-      <c r="G55" s="27">
+      <c r="G55" s="25">
         <f>Data!Q64</f>
         <v>10</v>
       </c>
-      <c r="H55" s="27">
+      <c r="H55" s="25">
         <f>Data!Q77</f>
         <v>10</v>
       </c>
     </row>
     <row r="56" ht="14.25">
-      <c r="C56" s="27">
+      <c r="C56" s="25">
         <f>Data!Q13</f>
         <v>10</v>
       </c>
-      <c r="D56" s="27">
+      <c r="D56" s="25">
         <f>Data!Q26</f>
         <v>10</v>
       </c>
-      <c r="E56" s="27">
+      <c r="E56" s="25">
         <f>Data!Q39</f>
         <v>10</v>
       </c>
-      <c r="F56" s="27">
+      <c r="F56" s="25">
         <f>Data!Q52</f>
         <v>10</v>
       </c>
-      <c r="G56" s="27">
+      <c r="G56" s="25">
         <f>Data!Q65</f>
         <v>10</v>
       </c>
-      <c r="H56" s="27">
+      <c r="H56" s="25">
         <f>Data!Q78</f>
         <v>10</v>
       </c>
     </row>
     <row r="57" ht="14.25">
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="27"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
+      <c r="H57" s="25"/>
     </row>
     <row r="58" ht="14.25">
       <c r="C58" t="s">
         <v>14</v>
       </c>
-      <c r="H58" s="29"/>
+      <c r="H58" s="28"/>
     </row>
     <row r="59" ht="14.25">
-      <c r="C59" s="30">
+      <c r="C59" s="29">
         <f>Data!R2</f>
         <v>3843</v>
       </c>
-      <c r="D59" s="30">
+      <c r="D59" s="29">
         <f>Data!R15</f>
         <v>16070</v>
       </c>
-      <c r="E59" s="30">
+      <c r="E59" s="29">
         <f>Data!R28</f>
         <v>7853</v>
       </c>
-      <c r="F59" s="30">
+      <c r="F59" s="29">
         <f>Data!R41</f>
         <v>4904</v>
       </c>
-      <c r="G59" s="30">
+      <c r="G59" s="29">
         <f>Data!R54</f>
         <v>11622</v>
       </c>
-      <c r="H59" s="30">
+      <c r="H59" s="29">
         <f>Data!R67</f>
-        <v>12014</v>
+        <v>8856</v>
       </c>
     </row>
     <row r="60" ht="14.25">
-      <c r="C60" s="30">
+      <c r="C60" s="29">
         <f>Data!R3</f>
         <v>6767</v>
       </c>
-      <c r="D60" s="30">
+      <c r="D60" s="29">
         <f>Data!R16</f>
         <v>1407</v>
       </c>
-      <c r="E60" s="30">
+      <c r="E60" s="29">
         <f>Data!R29</f>
         <v>5224</v>
       </c>
-      <c r="F60" s="30">
+      <c r="F60" s="29">
         <f>Data!R42</f>
         <v>2579</v>
       </c>
-      <c r="G60" s="30">
+      <c r="G60" s="29">
         <f>Data!R55</f>
         <v>7737</v>
       </c>
-      <c r="H60" s="30">
+      <c r="H60" s="29">
         <f>Data!R68</f>
-        <v>8713</v>
+        <v>8891</v>
       </c>
     </row>
     <row r="61" ht="14.25">
-      <c r="C61" s="30">
+      <c r="C61" s="29">
         <f>Data!R4</f>
         <v>65175</v>
       </c>
-      <c r="D61" s="30">
+      <c r="D61" s="29">
         <f>Data!R17</f>
         <v>163345</v>
       </c>
-      <c r="E61" s="30">
+      <c r="E61" s="29">
         <f>Data!R30</f>
         <v>42281</v>
       </c>
-      <c r="F61" s="30">
+      <c r="F61" s="29">
         <f>Data!R43</f>
         <v>101354</v>
       </c>
-      <c r="G61" s="30">
+      <c r="G61" s="29">
         <f>Data!R56</f>
         <v>316234</v>
       </c>
-      <c r="H61" s="30">
+      <c r="H61" s="29">
         <f>Data!R69</f>
-        <v>33906</v>
+        <v>449129</v>
       </c>
     </row>
     <row r="62" ht="14.25">
-      <c r="C62" s="30">
+      <c r="C62" s="29">
         <f>Data!R5</f>
         <v>22317</v>
       </c>
-      <c r="D62" s="30">
+      <c r="D62" s="29">
         <f>Data!R18</f>
         <v>39475</v>
       </c>
-      <c r="E62" s="30">
+      <c r="E62" s="29">
         <f>Data!R31</f>
         <v>26959</v>
       </c>
-      <c r="F62" s="30">
+      <c r="F62" s="29">
         <f>Data!R44</f>
         <v>18025</v>
       </c>
-      <c r="G62" s="30">
+      <c r="G62" s="29">
         <f>Data!R57</f>
         <v>37329</v>
       </c>
-      <c r="H62" s="30">
+      <c r="H62" s="29">
         <f>Data!R70</f>
-        <v>9168</v>
+        <v>79724</v>
       </c>
     </row>
     <row r="63" ht="14.25">
-      <c r="C63" s="30">
+      <c r="C63" s="29">
         <f>Data!R6</f>
         <v>750990</v>
       </c>
-      <c r="D63" s="30">
+      <c r="D63" s="29">
         <f>Data!R19</f>
         <v>631948</v>
       </c>
-      <c r="E63" s="30">
+      <c r="E63" s="29">
         <f>Data!R32</f>
         <v>472976</v>
       </c>
-      <c r="F63" s="30">
+      <c r="F63" s="29">
         <f>Data!R45</f>
         <v>273400</v>
       </c>
-      <c r="G63" s="30">
+      <c r="G63" s="29">
         <f>Data!R58</f>
         <v>4841618</v>
       </c>
-      <c r="H63" s="30">
+      <c r="H63" s="29">
         <f>Data!R71</f>
-        <v>793924</v>
+        <v>3152730</v>
       </c>
     </row>
     <row r="64" ht="14.25">
-      <c r="C64" s="30">
+      <c r="C64" s="29">
         <f>Data!R7</f>
         <v>56923</v>
       </c>
-      <c r="D64" s="30">
+      <c r="D64" s="29">
         <f>Data!R20</f>
         <v>128832</v>
       </c>
-      <c r="E64" s="30">
+      <c r="E64" s="29">
         <f>Data!R33</f>
         <v>71267</v>
       </c>
-      <c r="F64" s="30">
+      <c r="F64" s="29">
         <f>Data!R46</f>
         <v>28024</v>
       </c>
-      <c r="G64" s="30">
+      <c r="G64" s="29">
         <f>Data!R59</f>
         <v>408240</v>
       </c>
-      <c r="H64" s="30">
+      <c r="H64" s="29">
         <f>Data!R72</f>
-        <v>165995</v>
+        <v>415951</v>
       </c>
     </row>
     <row r="65" ht="14.25">
-      <c r="C65" s="30">
+      <c r="C65" s="29">
         <f>Data!R8</f>
         <v>800551</v>
       </c>
-      <c r="D65" s="30">
+      <c r="D65" s="29">
         <f>Data!R21</f>
         <v>570579</v>
       </c>
-      <c r="E65" s="30">
+      <c r="E65" s="29">
         <f>Data!R34</f>
         <v>466210</v>
       </c>
-      <c r="F65" s="30">
+      <c r="F65" s="29">
         <f>Data!R47</f>
         <v>365812</v>
       </c>
-      <c r="G65" s="30">
+      <c r="G65" s="29">
         <f>Data!R60</f>
         <v>5036289</v>
       </c>
-      <c r="H65" s="30">
+      <c r="H65" s="29">
         <f>Data!R73</f>
-        <v>695473</v>
+        <v>2505409</v>
       </c>
     </row>
     <row r="66" ht="14.25">
-      <c r="C66" s="30">
+      <c r="C66" s="29">
         <f>Data!R9</f>
         <v>123816</v>
       </c>
-      <c r="D66" s="30">
+      <c r="D66" s="29">
         <f>Data!R22</f>
         <v>49339</v>
       </c>
-      <c r="E66" s="30">
+      <c r="E66" s="29">
         <f>Data!R35</f>
         <v>41302</v>
       </c>
-      <c r="F66" s="30">
+      <c r="F66" s="29">
         <f>Data!R48</f>
         <v>29419</v>
       </c>
-      <c r="G66" s="30">
+      <c r="G66" s="29">
         <f>Data!R61</f>
         <v>292201</v>
       </c>
-      <c r="H66" s="30">
+      <c r="H66" s="29">
         <f>Data!R74</f>
-        <v>23944</v>
+        <v>334639</v>
       </c>
     </row>
     <row r="67" ht="14.25">
-      <c r="C67" s="30">
+      <c r="C67" s="29">
         <f>Data!R10</f>
         <v>226351</v>
       </c>
-      <c r="D67" s="30">
+      <c r="D67" s="29">
         <f>Data!R23</f>
         <v>195065</v>
       </c>
-      <c r="E67" s="30">
+      <c r="E67" s="29">
         <f>Data!R36</f>
         <v>134331</v>
       </c>
-      <c r="F67" s="30">
+      <c r="F67" s="29">
         <f>Data!R49</f>
         <v>99891</v>
       </c>
-      <c r="G67" s="30">
+      <c r="G67" s="29">
         <f>Data!R62</f>
         <v>1605390</v>
       </c>
-      <c r="H67" s="30">
+      <c r="H67" s="29">
         <f>Data!R75</f>
-        <v>235780</v>
+        <v>959261</v>
       </c>
     </row>
     <row r="68" ht="14.25">
-      <c r="C68" s="30">
+      <c r="C68" s="29">
         <f>Data!R11</f>
         <v>13790</v>
       </c>
-      <c r="D68" s="30">
+      <c r="D68" s="29">
         <f>Data!R24</f>
         <v>19209</v>
       </c>
-      <c r="E68" s="30">
+      <c r="E68" s="29">
         <f>Data!R37</f>
         <v>13450</v>
       </c>
-      <c r="F68" s="30">
+      <c r="F68" s="29">
         <f>Data!R50</f>
         <v>6718</v>
       </c>
-      <c r="G68" s="30">
+      <c r="G68" s="29">
         <f>Data!R63</f>
-        <v>20920</v>
-      </c>
-      <c r="H68" s="30">
+        <v>110279</v>
+      </c>
+      <c r="H68" s="29">
         <f>Data!R76</f>
-        <v>5165</v>
+        <v>59647</v>
       </c>
     </row>
     <row r="69" ht="14.25">
-      <c r="C69" s="30">
+      <c r="C69" s="29">
         <f>Data!R12</f>
         <v>13561</v>
       </c>
-      <c r="D69" s="30">
+      <c r="D69" s="29">
         <f>Data!R25</f>
         <v>5150</v>
       </c>
-      <c r="E69" s="30">
+      <c r="E69" s="29">
         <f>Data!R38</f>
         <v>2574</v>
       </c>
-      <c r="F69" s="30">
+      <c r="F69" s="29">
         <f>Data!R51</f>
         <v>2257</v>
       </c>
-      <c r="G69" s="30">
+      <c r="G69" s="29">
         <f>Data!R64</f>
-        <v>58958</v>
-      </c>
-      <c r="H69" s="30">
+        <v>286549</v>
+      </c>
+      <c r="H69" s="29">
         <f>Data!R77</f>
-        <v>23074</v>
+        <v>218984</v>
       </c>
     </row>
     <row r="70" ht="14.25">
-      <c r="C70" s="31">
+      <c r="C70" s="29">
         <f>Data!R13</f>
         <v>399</v>
       </c>
-      <c r="D70" s="30">
+      <c r="D70" s="29">
         <f>Data!R26</f>
         <v>1</v>
       </c>
-      <c r="E70" s="30">
+      <c r="E70" s="29">
         <f>Data!R39</f>
         <v>1</v>
       </c>
-      <c r="F70" s="30">
+      <c r="F70" s="29">
         <f>Data!R52</f>
         <v>1</v>
       </c>
-      <c r="G70" s="31">
+      <c r="G70" s="29">
         <f>Data!R65</f>
-        <v>15</v>
-      </c>
-      <c r="H70" s="31">
+        <v>3369</v>
+      </c>
+      <c r="H70" s="29">
         <f>Data!R78</f>
-        <v>3</v>
+        <v>867</v>
       </c>
     </row>
     <row r="71" ht="14.25">
-      <c r="C71" s="27"/>
-      <c r="D71" s="27"/>
-      <c r="E71" s="27"/>
-      <c r="F71" s="27"/>
-      <c r="G71" s="27"/>
-      <c r="H71" s="27"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="25"/>
+      <c r="E71" s="25"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="29"/>
+      <c r="H71" s="25"/>
     </row>
     <row r="72" ht="14.25">
+      <c r="G72" s="29"/>
       <c r="H72" s="19"/>
     </row>
     <row r="73" ht="14.25">
@@ -6489,7 +6540,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="4" rank="1" id="{00D00056-009D-44A0-B68B-002100C100DD}">
+          <x14:cfRule type="top10" priority="4" rank="1" id="{00BA0050-00F5-4EFF-B393-00C6004E00E8}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6502,7 +6553,7 @@
           <xm:sqref>H58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="3" bottom="1" rank="1" id="{00B10018-0066-4DDA-A23F-003F00E00061}">
+          <x14:cfRule type="top10" priority="3" bottom="1" rank="1" id="{006F0063-00FF-4C3E-8A5A-00BB00DC007D}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6515,7 +6566,7 @@
           <xm:sqref>H58</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{00DA0049-006C-4951-B8E1-0029000700C9}">
+          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{006A00B0-00A2-4F10-92E7-005400750014}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6528,7 +6579,7 @@
           <xm:sqref>C21:H22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="1" rank="1" id="{006D00B2-00EA-42C6-98B0-00A10020009D}">
+          <x14:cfRule type="top10" priority="1" rank="1" id="{00C000B0-0034-4D2E-A17C-005100AD00FD}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6541,7 +6592,124 @@
           <xm:sqref>C21:H22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{002F0092-00A3-4ECF-824E-009A005B00F7}">
+          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{000900B0-0073-4E84-999F-0005003F007A}">
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFF2DBDA"/>
+                  <bgColor rgb="FFF2DBDA"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>C35:H36</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="top10" priority="1" rank="1" id="{00E20052-00FE-41B2-9C9B-00D800890040}">
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFDBE5F1"/>
+                  <bgColor rgb="FFDBE5F1"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>C35:H36</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{006C000A-00D7-408D-8800-00C4000B00F9}">
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFF2DBDA"/>
+                  <bgColor rgb="FFF2DBDA"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>C59:H60</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="top10" priority="1" rank="1" id="{00CC00A1-00E7-449C-841E-00D800EC00C5}">
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFDBE5F1"/>
+                  <bgColor rgb="FFDBE5F1"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>C59:H60</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{00A900B6-007A-4B9B-A28F-00B8007400B4}">
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFF2DBDA"/>
+                  <bgColor rgb="FFF2DBDA"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>C41:H42</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="top10" priority="1" rank="1" id="{00B10038-00BF-4BFB-8CA9-001B0093004E}">
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFDBE5F1"/>
+                  <bgColor rgb="FFDBE5F1"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>C41:H42</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="top10" priority="1" rank="1" id="{001400ED-004A-4960-8210-004C0059000B}">
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFDBE5F1"/>
+                  <bgColor rgb="FFDBE5F1"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>C37:H38</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{000700EE-0092-4922-A723-00A9007C00DB}">
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFF2DBDA"/>
+                  <bgColor rgb="FFF2DBDA"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G71 G72</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="top10" priority="1" rank="1" id="{00430028-0072-46CD-A38B-002700D600A0}">
+            <x14:dxf>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFDBE5F1"/>
+                  <bgColor rgb="FFDBE5F1"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G71 G72</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{008400DC-00AC-48A1-90B0-00CC00E400AF}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6554,7 +6722,7 @@
           <xm:sqref>C23:H24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="1" rank="1" id="{000B001C-005A-4354-9B45-00BC00A90006}">
+          <x14:cfRule type="top10" priority="1" rank="1" id="{000A0020-0061-4412-B842-003300470053}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6567,7 +6735,7 @@
           <xm:sqref>C23:H24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{008D00F4-0057-4013-807E-00E30040008E}">
+          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{001B005D-009B-4248-A2B3-000C00470049}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6580,7 +6748,7 @@
           <xm:sqref>C25:H26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="1" rank="1" id="{006800B5-00E9-471C-A8CC-00A1001D0066}">
+          <x14:cfRule type="top10" priority="1" rank="1" id="{007E00CF-00C3-44A0-B5BB-009A004B0045}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6593,7 +6761,7 @@
           <xm:sqref>C25:H26</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{00F0006E-00DE-4556-9760-00B8007D00F9}">
+          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{00010008-002B-492A-A2D3-00330062006C}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6606,7 +6774,7 @@
           <xm:sqref>C27:H28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="1" rank="1" id="{00A10020-000D-4AF8-9E52-00A1006400C5}">
+          <x14:cfRule type="top10" priority="1" rank="1" id="{00F5006D-0086-4F2A-A5BD-00C300BE00D7}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6619,111 +6787,7 @@
           <xm:sqref>C27:H28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{00960042-00CD-4411-B11E-0008001600DF}">
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFF2DBDA"/>
-                  <bgColor rgb="FFF2DBDA"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>C35:H36</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="1" rank="1" id="{0013003E-007B-4101-8723-004D00A1006D}">
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFDBE5F1"/>
-                  <bgColor rgb="FFDBE5F1"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>C35:H36</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{00FC00F1-00F8-4EFD-8E26-00050051002B}">
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFF2DBDA"/>
-                  <bgColor rgb="FFF2DBDA"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>G37:H37</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="1" rank="1" id="{005B002F-0028-408F-ACCE-0077003900E6}">
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFDBE5F1"/>
-                  <bgColor rgb="FFDBE5F1"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>G37:H37</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{00DD003C-0074-4614-9526-001F00B10004}">
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFF2DBDA"/>
-                  <bgColor rgb="FFF2DBDA"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>C41:H42</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="1" rank="1" id="{00560054-0048-463D-A71D-002E00D300FA}">
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFDBE5F1"/>
-                  <bgColor rgb="FFDBE5F1"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>C41:H42</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{00390024-0096-468E-A309-000800FC00D4}">
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFF2DBDA"/>
-                  <bgColor rgb="FFF2DBDA"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>C59:H60</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="1" rank="1" id="{0021004E-0052-43E1-AC20-00C4005100B1}">
-            <x14:dxf>
-              <fill>
-                <patternFill patternType="solid">
-                  <fgColor rgb="FFDBE5F1"/>
-                  <bgColor rgb="FFDBE5F1"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>C59:H60</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{004B00E9-00F4-4AE4-9AFF-00B000380044}">
+          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{00AD00B7-006B-4B97-92F6-004900330017}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6736,7 +6800,7 @@
           <xm:sqref>C61:H62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="1" rank="1" id="{001900FF-00F9-4097-A022-00CB00DB0055}">
+          <x14:cfRule type="top10" priority="1" rank="1" id="{00030073-00D6-4D9E-B649-005800BC00AB}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6749,7 +6813,7 @@
           <xm:sqref>C61:H62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{0090000D-0063-4ACF-B672-004900A9003D}">
+          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{00D30082-00A6-4320-813F-009700F7008B}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6762,7 +6826,7 @@
           <xm:sqref>C63:H64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="1" rank="1" id="{00DB0087-0034-48B6-A5B1-001300D4006E}">
+          <x14:cfRule type="top10" priority="1" rank="1" id="{007E009A-0020-4D30-89A7-004200A400A1}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6775,7 +6839,7 @@
           <xm:sqref>C63:H64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{00C60052-00F6-4B49-950F-004400D400E9}">
+          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{006800C3-006A-4496-9814-00A7002A004B}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6788,7 +6852,7 @@
           <xm:sqref>C65:H66</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="1" rank="1" id="{00440047-0036-4DD8-AD9B-00AC00E200C5}">
+          <x14:cfRule type="top10" priority="1" rank="1" id="{007900DC-0011-4E4F-865A-00AA001200DB}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6801,7 +6865,7 @@
           <xm:sqref>C65:H66</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{00E900B6-0004-4E8A-8CC7-0051007E00AF}">
+          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{00A00013-0084-400A-AE18-0042008A0017}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6814,7 +6878,7 @@
           <xm:sqref>C67:H68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="1" rank="1" id="{007100E1-0075-46D6-86EB-00E900EA0064}">
+          <x14:cfRule type="top10" priority="1" rank="1" id="{004C0070-0097-44AC-A72B-00F900E300B9}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6827,7 +6891,7 @@
           <xm:sqref>C67:H68</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{0037007D-0022-440B-B9C3-006200AC0039}">
+          <x14:cfRule type="top10" priority="2" bottom="1" rank="1" id="{00F1004B-0000-40CE-9632-006F001300EF}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
@@ -6840,7 +6904,7 @@
           <xm:sqref>C69:H70</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="top10" priority="1" rank="1" id="{00BF0035-00A6-4FC8-AEEF-005A00100093}">
+          <x14:cfRule type="top10" priority="1" rank="1" id="{008900D1-00DD-473A-8B19-00D8003300DC}">
             <x14:dxf>
               <fill>
                 <patternFill patternType="solid">
